--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -1713,17 +1713,17 @@
       </c>
       <c r="B10" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="C10" s="2">
         <v>4272979.58</v>
       </c>
       <c r="D10" s="2">
-        <v>33928.56</v>
+        <v>13928.56</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>869958.859999999</v>
+        <v>889958.859999999</v>
       </c>
       <c r="F10" s="2">
         <v>151026.62</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="O10" s="2">
         <f t="shared" si="4"/>
-        <v>1109307.740084</v>
+        <v>1129307.740084</v>
       </c>
       <c r="P10" s="2">
         <v>2989500</v>
@@ -1782,14 +1782,14 @@
     <row r="11" spans="1:20">
       <c r="B11" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="8"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O11" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R11" s="2">
         <f t="shared" si="5"/>
@@ -1830,14 +1830,14 @@
     <row r="12" spans="1:20">
       <c r="B12" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="8"/>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="O12" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R12" s="2">
         <f t="shared" si="5"/>
@@ -1878,14 +1878,14 @@
     <row r="13" spans="1:20">
       <c r="B13" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="8"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="O13" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R13" s="2">
         <f t="shared" si="5"/>
@@ -1926,14 +1926,14 @@
     <row r="14" spans="1:20">
       <c r="B14" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="8"/>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R14" s="2">
         <f t="shared" si="5"/>
@@ -1974,14 +1974,14 @@
     <row r="15" spans="1:20">
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="8"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R15" s="2">
         <f t="shared" si="5"/>
@@ -2022,14 +2022,14 @@
     <row r="16" spans="1:20">
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
@@ -2070,14 +2070,14 @@
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2118,14 +2118,14 @@
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2166,14 +2166,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2214,14 +2214,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2262,14 +2262,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2310,14 +2310,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2358,14 +2358,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2406,14 +2406,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2454,14 +2454,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2502,14 +2502,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2550,14 +2550,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2598,14 +2598,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2646,14 +2646,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2694,14 +2694,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2742,14 +2742,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2790,14 +2790,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2838,14 +2838,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -2886,14 +2886,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -2934,14 +2934,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -2982,14 +2982,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3030,14 +3030,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3078,14 +3078,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3126,14 +3126,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3174,14 +3174,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3222,14 +3222,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3270,14 +3270,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3318,14 +3318,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3366,14 +3366,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3403020.72</v>
+        <v>3383020.72</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3403020.72</v>
+        <v>-3383020.72</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -1780,64 +1780,88 @@
       </c>
     </row>
     <row r="11" spans="1:20">
+      <c r="A11" s="1">
+        <v>46112</v>
+      </c>
       <c r="B11" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3626453.33</v>
       </c>
       <c r="D11" s="2">
-        <v>0</v>
+        <v>846.64</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>242585.969999999</v>
+      </c>
+      <c r="F11" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H11" s="2">
+        <v>31685.98</v>
+      </c>
       <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="2">
         <f t="shared" si="1"/>
-        <v>-3382.11</v>
+        <v>28303.87</v>
+      </c>
+      <c r="K11" s="2">
+        <v>11</v>
+      </c>
+      <c r="L11" s="3">
+        <v>6.9104</v>
       </c>
       <c r="M11" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>218962.796192</v>
       </c>
       <c r="N11" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>195591.063248</v>
       </c>
       <c r="O11" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>438177.033247999</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2989500</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>20900</v>
       </c>
       <c r="R11" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3845416.126192</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>876816.126192</v>
       </c>
       <c r="T11" s="2">
         <f t="shared" si="9"/>
-        <v>-1566909.103813</v>
+        <v>-690092.977621</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="B12" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="8"/>
@@ -1860,7 +1884,7 @@
       </c>
       <c r="O12" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R12" s="2">
         <f t="shared" si="5"/>
@@ -1872,20 +1896,20 @@
       </c>
       <c r="T12" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-876816.126192</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="B13" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="8"/>
@@ -1908,7 +1932,7 @@
       </c>
       <c r="O13" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R13" s="2">
         <f t="shared" si="5"/>
@@ -1926,14 +1950,14 @@
     <row r="14" spans="1:20">
       <c r="B14" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="8"/>
@@ -1956,7 +1980,7 @@
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R14" s="2">
         <f t="shared" si="5"/>
@@ -1974,14 +1998,14 @@
     <row r="15" spans="1:20">
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="8"/>
@@ -2004,7 +2028,7 @@
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R15" s="2">
         <f t="shared" si="5"/>
@@ -2022,14 +2046,14 @@
     <row r="16" spans="1:20">
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
@@ -2052,7 +2076,7 @@
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
@@ -2070,14 +2094,14 @@
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2100,7 +2124,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2118,14 +2142,14 @@
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2148,7 +2172,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2166,14 +2190,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2196,7 +2220,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2214,14 +2238,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2244,7 +2268,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2262,14 +2286,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2292,7 +2316,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2310,14 +2334,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2340,7 +2364,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2358,14 +2382,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2388,7 +2412,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2406,14 +2430,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2436,7 +2460,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2454,14 +2478,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2484,7 +2508,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2502,14 +2526,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2532,7 +2556,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2550,14 +2574,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2580,7 +2604,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2598,14 +2622,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2628,7 +2652,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2646,14 +2670,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2676,7 +2700,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2694,14 +2718,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2724,7 +2748,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2742,14 +2766,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2772,7 +2796,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2790,14 +2814,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2820,7 +2844,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2838,14 +2862,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2868,7 +2892,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -2886,14 +2910,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -2916,7 +2940,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -2934,14 +2958,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -2964,7 +2988,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -2982,14 +3006,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3012,7 +3036,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3030,14 +3054,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3060,7 +3084,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3078,14 +3102,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3108,7 +3132,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3126,14 +3150,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3156,7 +3180,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3174,14 +3198,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3204,7 +3228,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3222,14 +3246,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3252,7 +3276,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3270,14 +3294,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3300,7 +3324,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3318,14 +3342,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3348,7 +3372,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3366,14 +3390,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3383020.72</v>
+        <v>3383867.36</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3396,7 +3420,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3383020.72</v>
+        <v>-3383867.36</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="投资" sheetId="1" r:id="rId1"/>
@@ -1852,64 +1852,88 @@
       </c>
     </row>
     <row r="12" spans="1:20">
+      <c r="A12" s="1">
+        <v>46142</v>
+      </c>
       <c r="B12" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4125130.83</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>880.68</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>740382.789999999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G12" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H12" s="2">
+        <v>39715.02</v>
+      </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
       <c r="J12" s="2">
         <f t="shared" si="1"/>
-        <v>-3382.11</v>
+        <v>36332.91</v>
+      </c>
+      <c r="K12" s="2">
+        <v>11</v>
+      </c>
+      <c r="L12" s="3">
+        <v>6.8381</v>
       </c>
       <c r="M12" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>271575.278262</v>
       </c>
       <c r="N12" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>248448.071871</v>
       </c>
       <c r="O12" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>988830.861870999</v>
+      </c>
+      <c r="P12" s="2">
+        <v>2989500</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>21000</v>
       </c>
       <c r="R12" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4396706.108262</v>
       </c>
       <c r="S12" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1428206.108262</v>
       </c>
       <c r="T12" s="2">
         <f t="shared" si="9"/>
-        <v>-876816.126192</v>
+        <v>551389.982069999</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="B13" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="8"/>
@@ -1932,7 +1956,7 @@
       </c>
       <c r="O13" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R13" s="2">
         <f t="shared" si="5"/>
@@ -1944,20 +1968,20 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1428206.108262</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="B14" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="8"/>
@@ -1980,7 +2004,7 @@
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R14" s="2">
         <f t="shared" si="5"/>
@@ -1998,14 +2022,14 @@
     <row r="15" spans="1:20">
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="8"/>
@@ -2028,7 +2052,7 @@
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R15" s="2">
         <f t="shared" si="5"/>
@@ -2046,14 +2070,14 @@
     <row r="16" spans="1:20">
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
@@ -2076,7 +2100,7 @@
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
@@ -2094,14 +2118,14 @@
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2142,14 +2166,14 @@
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2172,7 +2196,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2190,14 +2214,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2220,7 +2244,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2238,14 +2262,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2268,7 +2292,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2286,14 +2310,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2316,7 +2340,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2334,14 +2358,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2364,7 +2388,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2382,14 +2406,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2412,7 +2436,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2430,14 +2454,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2460,7 +2484,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2478,14 +2502,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2508,7 +2532,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2526,14 +2550,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2556,7 +2580,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2574,14 +2598,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2604,7 +2628,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2622,14 +2646,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2652,7 +2676,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2670,14 +2694,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2700,7 +2724,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2718,14 +2742,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2748,7 +2772,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2766,14 +2790,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2796,7 +2820,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2814,14 +2838,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2844,7 +2868,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2862,14 +2886,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2892,7 +2916,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -2910,14 +2934,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -2940,7 +2964,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -2958,14 +2982,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -2988,7 +3012,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -3006,14 +3030,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3036,7 +3060,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3054,14 +3078,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3084,7 +3108,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3102,14 +3126,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3132,7 +3156,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3150,14 +3174,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3180,7 +3204,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3198,14 +3222,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3228,7 +3252,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3246,14 +3270,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3276,7 +3300,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3294,14 +3318,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3324,7 +3348,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3342,14 +3366,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3372,7 +3396,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3390,14 +3414,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3383867.36</v>
+        <v>3384748.04</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3420,7 +3444,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3383867.36</v>
+        <v>-3384748.04</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>
@@ -3445,8 +3469,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="2"/>
@@ -3573,6 +3597,26 @@
       </c>
       <c r="F6" s="2">
         <v>20900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B7" s="2">
+        <v>-220000</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-2407500</v>
+      </c>
+      <c r="D7" s="2">
+        <v>-82000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-280000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>21000</v>
       </c>
     </row>
   </sheetData>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -3469,8 +3469,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.75" style="2"/>
@@ -3616,6 +3616,26 @@
         <v>-280000</v>
       </c>
       <c r="F7" s="2">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B8" s="2">
+        <v>-270000</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-2407500</v>
+      </c>
+      <c r="D8" s="2">
+        <v>-82000</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-280000</v>
+      </c>
+      <c r="F8" s="2">
         <v>21000</v>
       </c>
     </row>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="投资" sheetId="1" r:id="rId1"/>
@@ -1924,64 +1924,88 @@
       </c>
     </row>
     <row r="13" spans="1:20">
+      <c r="A13" s="1">
+        <v>46171</v>
+      </c>
       <c r="B13" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3844905.6</v>
       </c>
       <c r="D13" s="2">
-        <v>0</v>
+        <v>50857.33</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>409300.229999999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G13" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H13" s="2">
+        <v>40703.26</v>
+      </c>
       <c r="I13" s="2">
         <v>0</v>
       </c>
       <c r="J13" s="2">
         <f t="shared" si="1"/>
-        <v>-3382.11</v>
+        <v>37321.15</v>
+      </c>
+      <c r="K13" s="2">
+        <v>11</v>
+      </c>
+      <c r="L13" s="3">
+        <v>6.7685</v>
       </c>
       <c r="M13" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>275500.01531</v>
       </c>
       <c r="N13" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>252608.203775</v>
       </c>
       <c r="O13" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>661908.433774999</v>
+      </c>
+      <c r="P13" s="2">
+        <v>3039500</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>21000</v>
       </c>
       <c r="R13" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4120405.61531</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1101905.61531</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="9"/>
-        <v>-1428206.108262</v>
+        <v>-326300.492951999</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="B14" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D14" s="2">
         <v>0</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="8"/>
@@ -2004,7 +2028,7 @@
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R14" s="2">
         <f t="shared" si="5"/>
@@ -2016,20 +2040,20 @@
       </c>
       <c r="T14" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1101905.61531</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="8"/>
@@ -2052,7 +2076,7 @@
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R15" s="2">
         <f t="shared" si="5"/>
@@ -2070,14 +2094,14 @@
     <row r="16" spans="1:20">
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
@@ -2100,7 +2124,7 @@
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
@@ -2118,14 +2142,14 @@
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2148,7 +2172,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2166,14 +2190,14 @@
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2196,7 +2220,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2214,14 +2238,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2244,7 +2268,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2262,14 +2286,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2292,7 +2316,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2310,14 +2334,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2340,7 +2364,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2358,14 +2382,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2388,7 +2412,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2406,14 +2430,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2436,7 +2460,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2454,14 +2478,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2484,7 +2508,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2502,14 +2526,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2532,7 +2556,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2550,14 +2574,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2580,7 +2604,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2598,14 +2622,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2628,7 +2652,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2646,14 +2670,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2676,7 +2700,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2694,14 +2718,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2724,7 +2748,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2742,14 +2766,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2772,7 +2796,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2790,14 +2814,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2820,7 +2844,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2838,14 +2862,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2868,7 +2892,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2886,14 +2910,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2916,7 +2940,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -2934,14 +2958,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -2964,7 +2988,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -2982,14 +3006,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -3012,7 +3036,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -3030,14 +3054,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3060,7 +3084,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3078,14 +3102,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3108,7 +3132,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3126,14 +3150,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3156,7 +3180,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3174,14 +3198,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3204,7 +3228,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3222,14 +3246,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3252,7 +3276,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3270,14 +3294,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3300,7 +3324,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3318,14 +3342,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3348,7 +3372,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3366,14 +3390,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3396,7 +3420,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3414,14 +3438,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3384748.04</v>
+        <v>3435605.37</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3444,7 +3468,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3384748.04</v>
+        <v>-3435605.37</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -1996,64 +1996,88 @@
       </c>
     </row>
     <row r="14" spans="1:20">
+      <c r="A14" s="1">
+        <v>46203</v>
+      </c>
       <c r="B14" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4127727.97</v>
       </c>
       <c r="D14" s="2">
-        <v>0</v>
+        <v>2486.68</v>
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>689635.919999999</v>
+      </c>
+      <c r="F14" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H14" s="2">
+        <v>29892.58</v>
+      </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14" s="2">
         <f t="shared" si="1"/>
-        <v>-3382.11</v>
+        <v>26510.47</v>
+      </c>
+      <c r="K14" s="2">
+        <v>11</v>
+      </c>
+      <c r="L14" s="3">
+        <v>6.7907</v>
       </c>
       <c r="M14" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>202991.543006</v>
       </c>
       <c r="N14" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>180024.648629</v>
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>869660.568628999</v>
+      </c>
+      <c r="P14" s="2">
+        <v>3039500</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>21100</v>
       </c>
       <c r="R14" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4330719.513006</v>
       </c>
       <c r="S14" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1312319.513006</v>
       </c>
       <c r="T14" s="2">
         <f t="shared" si="9"/>
-        <v>-1101905.61531</v>
+        <v>210413.897696</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="8"/>
@@ -2076,7 +2100,7 @@
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R15" s="2">
         <f t="shared" si="5"/>
@@ -2088,20 +2112,20 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1312319.513006</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
@@ -2124,7 +2148,7 @@
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
@@ -2142,14 +2166,14 @@
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2172,7 +2196,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2190,14 +2214,14 @@
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2220,7 +2244,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2238,14 +2262,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2268,7 +2292,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2286,14 +2310,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2316,7 +2340,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2334,14 +2358,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2364,7 +2388,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2382,14 +2406,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2412,7 +2436,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2430,14 +2454,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2460,7 +2484,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2478,14 +2502,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2508,7 +2532,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2526,14 +2550,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2556,7 +2580,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2574,14 +2598,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2604,7 +2628,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2622,14 +2646,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2652,7 +2676,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2670,14 +2694,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2700,7 +2724,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2718,14 +2742,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2748,7 +2772,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2766,14 +2790,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2796,7 +2820,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2814,14 +2838,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2844,7 +2868,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2862,14 +2886,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2892,7 +2916,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2910,14 +2934,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2940,7 +2964,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -2958,14 +2982,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -2988,7 +3012,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -3006,14 +3030,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -3036,7 +3060,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -3054,14 +3078,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3084,7 +3108,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3102,14 +3126,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3132,7 +3156,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3150,14 +3174,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3180,7 +3204,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3198,14 +3222,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3228,7 +3252,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3246,14 +3270,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3276,7 +3300,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3294,14 +3318,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3324,7 +3348,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3342,14 +3366,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3372,7 +3396,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3390,14 +3414,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3420,7 +3444,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3438,14 +3462,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3435605.37</v>
+        <v>3438092.05</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3468,7 +3492,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3435605.37</v>
+        <v>-3438092.05</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proj\FFMPEG\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -1507,7 +1512,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>410995.319999999</v>
+        <v>410995.32</v>
       </c>
       <c r="F7" s="2">
         <v>150279.96</v>
@@ -1542,7 +1547,7 @@
       </c>
       <c r="O7" s="2">
         <f t="shared" si="4"/>
-        <v>627930.829439999</v>
+        <v>627930.82944</v>
       </c>
       <c r="P7" s="2">
         <v>2979500</v>
@@ -1579,7 +1584,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>461271.419999999</v>
+        <v>461271.42</v>
       </c>
       <c r="F8" s="2">
         <v>151026.62</v>
@@ -1651,7 +1656,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>762788.459999999</v>
+        <v>762788.46</v>
       </c>
       <c r="F9" s="2">
         <v>151026.62</v>
@@ -1723,7 +1728,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>889958.859999999</v>
+        <v>889958.86</v>
       </c>
       <c r="F10" s="2">
         <v>151026.62</v>
@@ -1795,7 +1800,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>242585.969999999</v>
+        <v>242585.97</v>
       </c>
       <c r="F11" s="2">
         <v>151026.62</v>
@@ -1830,7 +1835,7 @@
       </c>
       <c r="O11" s="2">
         <f t="shared" si="4"/>
-        <v>438177.033247999</v>
+        <v>438177.033248</v>
       </c>
       <c r="P11" s="2">
         <v>2989500</v>
@@ -1867,7 +1872,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>740382.789999999</v>
+        <v>740382.79</v>
       </c>
       <c r="F12" s="2">
         <v>151026.62</v>
@@ -1902,7 +1907,7 @@
       </c>
       <c r="O12" s="2">
         <f t="shared" si="4"/>
-        <v>988830.861870999</v>
+        <v>988830.861871</v>
       </c>
       <c r="P12" s="2">
         <v>2989500</v>
@@ -1939,7 +1944,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>409300.229999999</v>
+        <v>409300.23</v>
       </c>
       <c r="F13" s="2">
         <v>151026.62</v>
@@ -1974,7 +1979,7 @@
       </c>
       <c r="O13" s="2">
         <f t="shared" si="4"/>
-        <v>661908.433774999</v>
+        <v>661908.433775</v>
       </c>
       <c r="P13" s="2">
         <v>3039500</v>
@@ -2011,7 +2016,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>689635.919999999</v>
+        <v>689635.92</v>
       </c>
       <c r="F14" s="2">
         <v>151026.62</v>
@@ -2046,7 +2051,7 @@
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>869660.568628999</v>
+        <v>869660.568629</v>
       </c>
       <c r="P14" s="2">
         <v>3039500</v>
@@ -2068,64 +2073,88 @@
       </c>
     </row>
     <row r="15" spans="1:20">
+      <c r="A15" s="1">
+        <v>46234</v>
+      </c>
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3904939.02</v>
       </c>
       <c r="D15" s="2">
-        <v>0</v>
+        <v>700.33</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>466146.64</v>
+      </c>
+      <c r="F15" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G15" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H15" s="2">
+        <v>30792.09</v>
+      </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15" s="2">
         <f t="shared" si="1"/>
-        <v>-3382.11</v>
+        <v>27409.98</v>
+      </c>
+      <c r="K15" s="2">
+        <v>11</v>
+      </c>
+      <c r="L15" s="3">
+        <v>6.7428</v>
       </c>
       <c r="M15" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>207624.904452</v>
       </c>
       <c r="N15" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>184820.013144</v>
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>650966.653144</v>
+      </c>
+      <c r="P15" s="2">
+        <v>3034500</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>21100</v>
       </c>
       <c r="R15" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4112563.924452</v>
       </c>
       <c r="S15" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1099163.924452</v>
       </c>
       <c r="T15" s="2">
         <f t="shared" si="9"/>
-        <v>-1312319.513006</v>
+        <v>-213155.588554</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
@@ -2148,7 +2177,7 @@
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
@@ -2160,20 +2189,20 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1099163.924452</v>
       </c>
     </row>
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2196,7 +2225,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2214,14 +2243,14 @@
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2244,7 +2273,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2262,14 +2291,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2292,7 +2321,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2310,14 +2339,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2340,7 +2369,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2358,14 +2387,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2388,7 +2417,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2406,14 +2435,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2436,7 +2465,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2454,14 +2483,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2484,7 +2513,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2502,14 +2531,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2532,7 +2561,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2550,14 +2579,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2580,7 +2609,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2598,14 +2627,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2628,7 +2657,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2646,14 +2675,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2676,7 +2705,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2694,14 +2723,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2724,7 +2753,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2742,14 +2771,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2772,7 +2801,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2790,14 +2819,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2820,7 +2849,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2838,14 +2867,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2868,7 +2897,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2886,14 +2915,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2916,7 +2945,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2934,14 +2963,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2964,7 +2993,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -2982,14 +3011,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -3012,7 +3041,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -3030,14 +3059,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -3060,7 +3089,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -3078,14 +3107,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3108,7 +3137,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3126,14 +3155,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3156,7 +3185,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3174,14 +3203,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3204,7 +3233,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3222,14 +3251,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3252,7 +3281,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3270,14 +3299,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3300,7 +3329,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3318,14 +3347,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3348,7 +3377,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3366,14 +3395,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3396,7 +3425,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3414,14 +3443,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3444,7 +3473,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3462,14 +3491,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3438092.05</v>
+        <v>3438792.38</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3492,7 +3521,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3438092.05</v>
+        <v>-3438792.38</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>

--- a/资产负债表.xlsx
+++ b/资产负债表.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>410995.32</v>
+        <v>410995.319999999</v>
       </c>
       <c r="F7" s="2">
         <v>150279.96</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="O7" s="2">
         <f t="shared" si="4"/>
-        <v>627930.82944</v>
+        <v>627930.829439999</v>
       </c>
       <c r="P7" s="2">
         <v>2979500</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>461271.42</v>
+        <v>461271.419999999</v>
       </c>
       <c r="F8" s="2">
         <v>151026.62</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>762788.46</v>
+        <v>762788.459999999</v>
       </c>
       <c r="F9" s="2">
         <v>151026.62</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>889958.86</v>
+        <v>889958.859999999</v>
       </c>
       <c r="F10" s="2">
         <v>151026.62</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>242585.97</v>
+        <v>242585.969999999</v>
       </c>
       <c r="F11" s="2">
         <v>151026.62</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O11" s="2">
         <f t="shared" si="4"/>
-        <v>438177.033248</v>
+        <v>438177.033247999</v>
       </c>
       <c r="P11" s="2">
         <v>2989500</v>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>740382.79</v>
+        <v>740382.789999999</v>
       </c>
       <c r="F12" s="2">
         <v>151026.62</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="O12" s="2">
         <f t="shared" si="4"/>
-        <v>988830.861871</v>
+        <v>988830.861870999</v>
       </c>
       <c r="P12" s="2">
         <v>2989500</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>409300.23</v>
+        <v>409300.229999999</v>
       </c>
       <c r="F13" s="2">
         <v>151026.62</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="O13" s="2">
         <f t="shared" si="4"/>
-        <v>661908.433775</v>
+        <v>661908.433774999</v>
       </c>
       <c r="P13" s="2">
         <v>3039500</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" si="0"/>
-        <v>689635.92</v>
+        <v>689635.919999999</v>
       </c>
       <c r="F14" s="2">
         <v>151026.62</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="O14" s="2">
         <f t="shared" si="4"/>
-        <v>869660.568629</v>
+        <v>869660.568628999</v>
       </c>
       <c r="P14" s="2">
         <v>3039500</v>
@@ -2078,17 +2078,17 @@
       </c>
       <c r="B15" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3438995.38</v>
       </c>
       <c r="C15" s="2">
         <v>3904939.02</v>
       </c>
       <c r="D15" s="2">
-        <v>700.33</v>
+        <v>903.33</v>
       </c>
       <c r="E15" s="2">
         <f t="shared" si="0"/>
-        <v>466146.64</v>
+        <v>465943.639999999</v>
       </c>
       <c r="F15" s="2">
         <v>151026.62</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="O15" s="2">
         <f t="shared" si="4"/>
-        <v>650966.653144</v>
+        <v>650763.653143999</v>
       </c>
       <c r="P15" s="2">
         <v>3034500</v>
@@ -2145,64 +2145,88 @@
       </c>
     </row>
     <row r="16" spans="1:20">
+      <c r="A16" s="1">
+        <v>46265</v>
+      </c>
       <c r="B16" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4069656.66</v>
       </c>
       <c r="D16" s="2">
-        <v>0</v>
+        <v>911.62</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>629749.659999999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>151026.62</v>
       </c>
       <c r="G16" s="2">
         <f t="shared" si="8"/>
         <v>3382.11</v>
       </c>
+      <c r="H16" s="2">
+        <v>31681.54</v>
+      </c>
       <c r="I16" s="2">
         <v>0</v>
       </c>
       <c r="J16" s="2">
         <f t="shared" si="1"/>
-        <v>-3382.11</v>
+        <v>28299.43</v>
+      </c>
+      <c r="K16" s="2">
+        <v>11</v>
+      </c>
+      <c r="L16" s="3">
+        <v>6.7203</v>
       </c>
       <c r="M16" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>212909.453262</v>
       </c>
       <c r="N16" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>190180.659429</v>
       </c>
       <c r="O16" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>819930.319428999</v>
+      </c>
+      <c r="P16" s="2">
+        <v>3034500</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>21100</v>
       </c>
       <c r="R16" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4282566.113262</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1269166.113262</v>
       </c>
       <c r="T16" s="2">
         <f t="shared" si="9"/>
-        <v>-1099163.924452</v>
+        <v>170002.188810001</v>
       </c>
     </row>
     <row r="17" spans="2:20">
       <c r="B17" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="8"/>
@@ -2225,7 +2249,7 @@
       </c>
       <c r="O17" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R17" s="2">
         <f t="shared" si="5"/>
@@ -2237,20 +2261,20 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-1269166.113262</v>
       </c>
     </row>
     <row r="18" spans="2:20">
       <c r="B18" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G18" s="2">
         <f t="shared" si="8"/>
@@ -2273,7 +2297,7 @@
       </c>
       <c r="O18" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R18" s="2">
         <f t="shared" si="5"/>
@@ -2291,14 +2315,14 @@
     <row r="19" spans="2:20">
       <c r="B19" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="8"/>
@@ -2321,7 +2345,7 @@
       </c>
       <c r="O19" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R19" s="2">
         <f t="shared" si="5"/>
@@ -2339,14 +2363,14 @@
     <row r="20" spans="2:20">
       <c r="B20" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G20" s="2">
         <f t="shared" si="8"/>
@@ -2369,7 +2393,7 @@
       </c>
       <c r="O20" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="5"/>
@@ -2387,14 +2411,14 @@
     <row r="21" spans="2:20">
       <c r="B21" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G21" s="2">
         <f t="shared" si="8"/>
@@ -2417,7 +2441,7 @@
       </c>
       <c r="O21" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R21" s="2">
         <f t="shared" si="5"/>
@@ -2435,14 +2459,14 @@
     <row r="22" spans="2:20">
       <c r="B22" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G22" s="2">
         <f t="shared" si="8"/>
@@ -2465,7 +2489,7 @@
       </c>
       <c r="O22" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R22" s="2">
         <f t="shared" si="5"/>
@@ -2483,14 +2507,14 @@
     <row r="23" spans="2:20">
       <c r="B23" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G23" s="2">
         <f t="shared" si="8"/>
@@ -2513,7 +2537,7 @@
       </c>
       <c r="O23" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R23" s="2">
         <f t="shared" si="5"/>
@@ -2531,14 +2555,14 @@
     <row r="24" spans="2:20">
       <c r="B24" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
       </c>
       <c r="E24" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G24" s="2">
         <f t="shared" si="8"/>
@@ -2561,7 +2585,7 @@
       </c>
       <c r="O24" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R24" s="2">
         <f t="shared" si="5"/>
@@ -2579,14 +2603,14 @@
     <row r="25" spans="2:20">
       <c r="B25" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G25" s="2">
         <f t="shared" si="8"/>
@@ -2609,7 +2633,7 @@
       </c>
       <c r="O25" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R25" s="2">
         <f t="shared" si="5"/>
@@ -2627,14 +2651,14 @@
     <row r="26" spans="2:20">
       <c r="B26" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G26" s="2">
         <f t="shared" si="8"/>
@@ -2657,7 +2681,7 @@
       </c>
       <c r="O26" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R26" s="2">
         <f t="shared" si="5"/>
@@ -2675,14 +2699,14 @@
     <row r="27" spans="2:20">
       <c r="B27" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G27" s="2">
         <f t="shared" si="8"/>
@@ -2705,7 +2729,7 @@
       </c>
       <c r="O27" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R27" s="2">
         <f t="shared" si="5"/>
@@ -2723,14 +2747,14 @@
     <row r="28" spans="2:20">
       <c r="B28" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G28" s="2">
         <f t="shared" si="8"/>
@@ -2753,7 +2777,7 @@
       </c>
       <c r="O28" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="5"/>
@@ -2771,14 +2795,14 @@
     <row r="29" spans="2:20">
       <c r="B29" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G29" s="2">
         <f t="shared" si="8"/>
@@ -2801,7 +2825,7 @@
       </c>
       <c r="O29" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R29" s="2">
         <f t="shared" si="5"/>
@@ -2819,14 +2843,14 @@
     <row r="30" spans="2:20">
       <c r="B30" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G30" s="2">
         <f t="shared" si="8"/>
@@ -2849,7 +2873,7 @@
       </c>
       <c r="O30" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R30" s="2">
         <f t="shared" si="5"/>
@@ -2867,14 +2891,14 @@
     <row r="31" spans="2:20">
       <c r="B31" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="8"/>
@@ -2897,7 +2921,7 @@
       </c>
       <c r="O31" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R31" s="2">
         <f t="shared" si="5"/>
@@ -2915,14 +2939,14 @@
     <row r="32" spans="2:20">
       <c r="B32" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
       </c>
       <c r="E32" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G32" s="2">
         <f t="shared" si="8"/>
@@ -2945,7 +2969,7 @@
       </c>
       <c r="O32" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R32" s="2">
         <f t="shared" si="5"/>
@@ -2963,14 +2987,14 @@
     <row r="33" spans="2:20">
       <c r="B33" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
       </c>
       <c r="E33" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G33" s="2">
         <f t="shared" si="8"/>
@@ -2993,7 +3017,7 @@
       </c>
       <c r="O33" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R33" s="2">
         <f t="shared" si="5"/>
@@ -3011,14 +3035,14 @@
     <row r="34" spans="2:20">
       <c r="B34" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
       </c>
       <c r="E34" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G34" s="2">
         <f t="shared" si="8"/>
@@ -3041,7 +3065,7 @@
       </c>
       <c r="O34" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R34" s="2">
         <f t="shared" si="5"/>
@@ -3059,14 +3083,14 @@
     <row r="35" spans="2:20">
       <c r="B35" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G35" s="2">
         <f t="shared" si="8"/>
@@ -3089,7 +3113,7 @@
       </c>
       <c r="O35" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R35" s="2">
         <f t="shared" si="5"/>
@@ -3107,14 +3131,14 @@
     <row r="36" spans="2:20">
       <c r="B36" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="8"/>
@@ -3137,7 +3161,7 @@
       </c>
       <c r="O36" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R36" s="2">
         <f t="shared" si="5"/>
@@ -3155,14 +3179,14 @@
     <row r="37" spans="2:20">
       <c r="B37" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="8"/>
@@ -3185,7 +3209,7 @@
       </c>
       <c r="O37" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R37" s="2">
         <f t="shared" si="5"/>
@@ -3203,14 +3227,14 @@
     <row r="38" spans="2:20">
       <c r="B38" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="8"/>
@@ -3233,7 +3257,7 @@
       </c>
       <c r="O38" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R38" s="2">
         <f t="shared" si="5"/>
@@ -3251,14 +3275,14 @@
     <row r="39" spans="2:20">
       <c r="B39" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="8"/>
@@ -3281,7 +3305,7 @@
       </c>
       <c r="O39" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="5"/>
@@ -3299,14 +3323,14 @@
     <row r="40" spans="2:20">
       <c r="B40" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G40" s="2">
         <f t="shared" si="8"/>
@@ -3329,7 +3353,7 @@
       </c>
       <c r="O40" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R40" s="2">
         <f t="shared" si="5"/>
@@ -3347,14 +3371,14 @@
     <row r="41" spans="2:20">
       <c r="B41" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G41" s="2">
         <f t="shared" si="8"/>
@@ -3377,7 +3401,7 @@
       </c>
       <c r="O41" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R41" s="2">
         <f t="shared" si="5"/>
@@ -3395,14 +3419,14 @@
     <row r="42" spans="2:20">
       <c r="B42" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G42" s="2">
         <f t="shared" si="8"/>
@@ -3425,7 +3449,7 @@
       </c>
       <c r="O42" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R42" s="2">
         <f t="shared" si="5"/>
@@ -3443,14 +3467,14 @@
     <row r="43" spans="2:20">
       <c r="B43" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
       </c>
       <c r="E43" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G43" s="2">
         <f t="shared" si="8"/>
@@ -3473,7 +3497,7 @@
       </c>
       <c r="O43" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
@@ -3491,14 +3515,14 @@
     <row r="44" spans="2:20">
       <c r="B44" s="2">
         <f t="shared" si="7"/>
-        <v>3438792.38</v>
+        <v>3439907</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
       </c>
       <c r="E44" s="2">
         <f t="shared" si="0"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="G44" s="2">
         <f t="shared" si="8"/>
@@ -3521,7 +3545,7 @@
       </c>
       <c r="O44" s="2">
         <f t="shared" si="4"/>
-        <v>-3438792.38</v>
+        <v>-3439907</v>
       </c>
       <c r="R44" s="2">
         <f t="shared" si="5"/>
